--- a/artfynd/A 4778-2025 artfynd.xlsx
+++ b/artfynd/A 4778-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611368</v>
+        <v>122611363</v>
       </c>
       <c r="B2" t="n">
         <v>98237</v>
@@ -709,7 +709,11 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577815</v>
+        <v>577813</v>
       </c>
       <c r="R2" t="n">
-        <v>6433859</v>
+        <v>6433858</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611363</v>
+        <v>122611368</v>
       </c>
       <c r="B3" t="n">
         <v>98237</v>
@@ -816,11 +820,7 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577813</v>
+        <v>577815</v>
       </c>
       <c r="R3" t="n">
-        <v>6433858</v>
+        <v>6433859</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 4778-2025 artfynd.xlsx
+++ b/artfynd/A 4778-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122611363</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>122611368</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4778-2025 artfynd.xlsx
+++ b/artfynd/A 4778-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611363</v>
+        <v>122611368</v>
       </c>
       <c r="B2" t="n">
         <v>98240</v>
@@ -709,11 +709,7 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577813</v>
+        <v>577815</v>
       </c>
       <c r="R2" t="n">
-        <v>6433858</v>
+        <v>6433859</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611368</v>
+        <v>122611363</v>
       </c>
       <c r="B3" t="n">
         <v>98240</v>
@@ -820,7 +816,11 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577815</v>
+        <v>577813</v>
       </c>
       <c r="R3" t="n">
-        <v>6433859</v>
+        <v>6433858</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 4778-2025 artfynd.xlsx
+++ b/artfynd/A 4778-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122611368</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>122611363</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4778-2025 artfynd.xlsx
+++ b/artfynd/A 4778-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122611368</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>122611363</v>
       </c>
       <c r="B3" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4778-2025 artfynd.xlsx
+++ b/artfynd/A 4778-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611368</v>
+        <v>122611363</v>
       </c>
       <c r="B2" t="n">
         <v>98244</v>
@@ -709,7 +709,11 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577815</v>
+        <v>577813</v>
       </c>
       <c r="R2" t="n">
-        <v>6433859</v>
+        <v>6433858</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611363</v>
+        <v>122611368</v>
       </c>
       <c r="B3" t="n">
         <v>98244</v>
@@ -816,11 +820,7 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577813</v>
+        <v>577815</v>
       </c>
       <c r="R3" t="n">
-        <v>6433858</v>
+        <v>6433859</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 4778-2025 artfynd.xlsx
+++ b/artfynd/A 4778-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122611363</v>
       </c>
       <c r="B2" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>122611368</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4778-2025 artfynd.xlsx
+++ b/artfynd/A 4778-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611363</v>
+        <v>122611368</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,11 +709,7 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577813</v>
+        <v>577815</v>
       </c>
       <c r="R2" t="n">
-        <v>6433858</v>
+        <v>6433859</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611368</v>
+        <v>122611363</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,7 +816,11 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577815</v>
+        <v>577813</v>
       </c>
       <c r="R3" t="n">
-        <v>6433859</v>
+        <v>6433858</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 4778-2025 artfynd.xlsx
+++ b/artfynd/A 4778-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611368</v>
+        <v>122611363</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,7 +709,11 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577815</v>
+        <v>577813</v>
       </c>
       <c r="R2" t="n">
-        <v>6433859</v>
+        <v>6433858</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611363</v>
+        <v>122611368</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,11 +820,7 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577813</v>
+        <v>577815</v>
       </c>
       <c r="R3" t="n">
-        <v>6433858</v>
+        <v>6433859</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 4778-2025 artfynd.xlsx
+++ b/artfynd/A 4778-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611363</v>
+        <v>122611368</v>
       </c>
       <c r="B2" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,11 +709,7 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577813</v>
+        <v>577815</v>
       </c>
       <c r="R2" t="n">
-        <v>6433858</v>
+        <v>6433859</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611368</v>
+        <v>122611363</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,7 +816,11 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577815</v>
+        <v>577813</v>
       </c>
       <c r="R3" t="n">
-        <v>6433859</v>
+        <v>6433858</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 4778-2025 artfynd.xlsx
+++ b/artfynd/A 4778-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,6 +891,120 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126166294</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 4750, Kulla, Hyllela, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>577824</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6433871</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även sång. Trol fler än 2,</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4778-2025 artfynd.xlsx
+++ b/artfynd/A 4778-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>126166294</v>
       </c>
       <c r="B4" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4778-2025 artfynd.xlsx
+++ b/artfynd/A 4778-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>126166294</v>
       </c>
       <c r="B4" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4778-2025 artfynd.xlsx
+++ b/artfynd/A 4778-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>126166294</v>
       </c>
       <c r="B4" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4778-2025 artfynd.xlsx
+++ b/artfynd/A 4778-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611368</v>
+        <v>122611398</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 4778, Kulla, Hyllela, Sm</t>
+          <t>A 4750, Kulla, Hyllela, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577815</v>
+        <v>577758</v>
       </c>
       <c r="R2" t="n">
-        <v>6433859</v>
+        <v>6433794</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,61 +784,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611363</v>
+        <v>126166294</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 4778, Kulla, Hyllela, Sm</t>
+          <t>A 4750, Kulla, Hyllela, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577813</v>
+        <v>577824</v>
       </c>
       <c r="R3" t="n">
-        <v>6433858</v>
+        <v>6433871</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +861,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Även sång. Trol fler än 2,</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,7 +880,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,67 +891,63 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126166294</v>
+        <v>122611363</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 4750, Kulla, Hyllela, Sm</t>
+          <t>A 4778, Kulla, Hyllela, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577824</v>
+        <v>577813</v>
       </c>
       <c r="R4" t="n">
-        <v>6433871</v>
+        <v>6433858</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,17 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även sång. Trol fler än 2,</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,6 +985,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1000,10 +997,112 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122611368</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 4778, Kulla, Hyllela, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>577815</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6433859</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
